--- a/output/roomself_excel/1862.xlsx
+++ b/output/roomself_excel/1862.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,20 +466,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Kitchen</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>289044</v>
+        <v>116875</v>
       </c>
       <c r="D2" t="n">
-        <v>4972</v>
+        <v>2800</v>
       </c>
       <c r="E2" t="n">
-        <v>1095</v>
+        <v>738</v>
       </c>
       <c r="F2" t="n">
-        <v>1007</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3">
@@ -488,20 +488,20 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Living Room</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>254100</v>
+        <v>277325</v>
       </c>
       <c r="D3" t="n">
-        <v>4796</v>
+        <v>4308</v>
       </c>
       <c r="E3" t="n">
         <v>984</v>
       </c>
       <c r="F3" t="n">
-        <v>275</v>
+        <v>739</v>
       </c>
     </row>
     <row r="4">
@@ -532,20 +532,20 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hallway</t>
+          <t>Bedroom</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>237341</v>
+        <v>160528</v>
       </c>
       <c r="D5" t="n">
-        <v>5760</v>
+        <v>3296</v>
       </c>
       <c r="E5" t="n">
-        <v>991</v>
+        <v>508</v>
       </c>
       <c r="F5" t="n">
-        <v>362</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6">
@@ -558,16 +558,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>160528</v>
+        <v>132468</v>
       </c>
       <c r="D6" t="n">
-        <v>3296</v>
+        <v>3547</v>
       </c>
       <c r="E6" t="n">
-        <v>508</v>
+        <v>169</v>
       </c>
       <c r="F6" t="n">
-        <v>53</v>
+        <v>155</v>
       </c>
     </row>
     <row r="7">
@@ -576,20 +576,20 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Living Room</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>673379</v>
+        <v>26196</v>
       </c>
       <c r="D7" t="n">
-        <v>13152</v>
+        <v>1360</v>
       </c>
       <c r="E7" t="n">
-        <v>984</v>
+        <v>222</v>
       </c>
       <c r="F7" t="n">
-        <v>958</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -598,20 +598,20 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bath</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>94800</v>
+        <v>24080</v>
       </c>
       <c r="D8" t="n">
-        <v>2464</v>
+        <v>1248</v>
       </c>
       <c r="E8" t="n">
-        <v>991</v>
+        <v>172</v>
       </c>
       <c r="F8" t="n">
-        <v>348</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -624,16 +624,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>26196</v>
+        <v>70311</v>
       </c>
       <c r="D9" t="n">
-        <v>1360</v>
+        <v>2384</v>
       </c>
       <c r="E9" t="n">
-        <v>222</v>
+        <v>457</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>416</v>
       </c>
     </row>
     <row r="10">
@@ -646,16 +646,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>24080</v>
+        <v>23961</v>
       </c>
       <c r="D10" t="n">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="E10" t="n">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="F10" t="n">
-        <v>22</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11">
@@ -664,20 +664,20 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>70311</v>
+        <v>237341</v>
       </c>
       <c r="D11" t="n">
-        <v>2384</v>
+        <v>5760</v>
       </c>
       <c r="E11" t="n">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="F11" t="n">
-        <v>416</v>
+        <v>362</v>
       </c>
     </row>
     <row r="12">
@@ -686,20 +686,20 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Bath</t>
+          <t>Hallway</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>23961</v>
+        <v>146711</v>
       </c>
       <c r="D12" t="n">
-        <v>1240</v>
+        <v>5389</v>
       </c>
       <c r="E12" t="n">
-        <v>147</v>
+        <v>299</v>
       </c>
       <c r="F12" t="n">
-        <v>48</v>
+        <v>219</v>
       </c>
     </row>
     <row r="13">
@@ -708,20 +708,20 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Storage</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>36360</v>
+        <v>43758</v>
       </c>
       <c r="D13" t="n">
-        <v>1528</v>
+        <v>1684</v>
       </c>
       <c r="E13" t="n">
-        <v>991</v>
+        <v>187</v>
       </c>
       <c r="F13" t="n">
-        <v>234</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -730,20 +730,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Storage</t>
+          <t>Garage</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>43758</v>
+        <v>300447</v>
       </c>
       <c r="D14" t="n">
-        <v>1684</v>
+        <v>3627</v>
       </c>
       <c r="E14" t="n">
-        <v>983</v>
+        <v>298</v>
       </c>
       <c r="F14" t="n">
-        <v>187</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -752,20 +752,108 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Garage</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>423337</v>
+        <v>289044</v>
       </c>
       <c r="D15" t="n">
-        <v>6388</v>
+        <v>4972</v>
       </c>
       <c r="E15" t="n">
-        <v>1373</v>
+        <v>1007</v>
       </c>
       <c r="F15" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>254100</v>
+      </c>
+      <c r="D16" t="n">
+        <v>4796</v>
+      </c>
+      <c r="E16" t="n">
         <v>984</v>
+      </c>
+      <c r="F16" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>94800</v>
+      </c>
+      <c r="D17" t="n">
+        <v>2464</v>
+      </c>
+      <c r="E17" t="n">
+        <v>362</v>
+      </c>
+      <c r="F17" t="n">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>36360</v>
+      </c>
+      <c r="D18" t="n">
+        <v>1528</v>
+      </c>
+      <c r="E18" t="n">
+        <v>292</v>
+      </c>
+      <c r="F18" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Other</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>122890</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3363</v>
+      </c>
+      <c r="E19" t="n">
+        <v>983</v>
+      </c>
+      <c r="F19" t="n">
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/output/roomself_excel/1862.xlsx
+++ b/output/roomself_excel/1862.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,47 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallLength</t>
+          <t>WallDir_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>ExtWallWidth</t>
+          <t>ExtWallLength_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>WallDir_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallLength_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>ExtWallWidth_3</t>
         </is>
       </c>
     </row>
@@ -475,12 +510,23 @@
       <c r="D2" t="n">
         <v>2800</v>
       </c>
-      <c r="E2" t="n">
-        <v>738</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F2" t="n">
-        <v>23</v>
-      </c>
+        <v>425</v>
+      </c>
+      <c r="G2" t="n">
+        <v>22</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -497,12 +543,23 @@
       <c r="D3" t="n">
         <v>4308</v>
       </c>
-      <c r="E3" t="n">
-        <v>984</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F3" t="n">
-        <v>739</v>
-      </c>
+        <v>426</v>
+      </c>
+      <c r="G3" t="n">
+        <v>35</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -519,12 +576,23 @@
       <c r="D4" t="n">
         <v>3064</v>
       </c>
-      <c r="E4" t="n">
-        <v>733</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F4" t="n">
-        <v>28</v>
-      </c>
+        <v>508</v>
+      </c>
+      <c r="G4" t="n">
+        <v>24</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,12 +609,31 @@
       <c r="D5" t="n">
         <v>3296</v>
       </c>
-      <c r="E5" t="n">
-        <v>508</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F5" t="n">
+        <v>227</v>
+      </c>
+      <c r="G5" t="n">
         <v>53</v>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>281</v>
+      </c>
+      <c r="J5" t="n">
+        <v>46</v>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -563,12 +650,23 @@
       <c r="D6" t="n">
         <v>3547</v>
       </c>
-      <c r="E6" t="n">
-        <v>169</v>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F6" t="n">
-        <v>155</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="G6" t="n">
+        <v>35</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -585,12 +683,23 @@
       <c r="D7" t="n">
         <v>1360</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
         <v>222</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>35</v>
       </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -607,12 +716,23 @@
       <c r="D8" t="n">
         <v>1248</v>
       </c>
-      <c r="E8" t="n">
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
         <v>172</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>22</v>
       </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -629,12 +749,31 @@
       <c r="D9" t="n">
         <v>2384</v>
       </c>
-      <c r="E9" t="n">
-        <v>457</v>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F9" t="n">
-        <v>416</v>
-      </c>
+        <v>162</v>
+      </c>
+      <c r="G9" t="n">
+        <v>24</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>165</v>
+      </c>
+      <c r="J9" t="n">
+        <v>48</v>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -651,12 +790,23 @@
       <c r="D10" t="n">
         <v>1240</v>
       </c>
-      <c r="E10" t="n">
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
         <v>147</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>48</v>
       </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -673,12 +823,23 @@
       <c r="D11" t="n">
         <v>5760</v>
       </c>
-      <c r="E11" t="n">
-        <v>468</v>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F11" t="n">
-        <v>362</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="G11" t="n">
+        <v>24</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,12 +856,31 @@
       <c r="D12" t="n">
         <v>5389</v>
       </c>
-      <c r="E12" t="n">
-        <v>299</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F12" t="n">
-        <v>219</v>
-      </c>
+        <v>192</v>
+      </c>
+      <c r="G12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -717,12 +897,23 @@
       <c r="D13" t="n">
         <v>1684</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
         <v>187</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>22</v>
       </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -739,12 +930,23 @@
       <c r="D14" t="n">
         <v>3627</v>
       </c>
-      <c r="E14" t="n">
-        <v>298</v>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
       </c>
       <c r="F14" t="n">
-        <v>14</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -761,12 +963,31 @@
       <c r="D15" t="n">
         <v>4972</v>
       </c>
-      <c r="E15" t="n">
-        <v>1007</v>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F15" t="n">
         <v>186</v>
       </c>
+      <c r="G15" t="n">
+        <v>36</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>186</v>
+      </c>
+      <c r="J15" t="n">
+        <v>39</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -783,12 +1004,31 @@
       <c r="D16" t="n">
         <v>4796</v>
       </c>
-      <c r="E16" t="n">
-        <v>984</v>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F16" t="n">
         <v>275</v>
       </c>
+      <c r="G16" t="n">
+        <v>24</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>275</v>
+      </c>
+      <c r="J16" t="n">
+        <v>36</v>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -805,12 +1045,31 @@
       <c r="D17" t="n">
         <v>2464</v>
       </c>
-      <c r="E17" t="n">
-        <v>362</v>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F17" t="n">
-        <v>348</v>
-      </c>
+        <v>300</v>
+      </c>
+      <c r="G17" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>316</v>
+      </c>
+      <c r="J17" t="n">
+        <v>48</v>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -827,11 +1086,38 @@
       <c r="D18" t="n">
         <v>1528</v>
       </c>
-      <c r="E18" t="n">
-        <v>292</v>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F18" t="n">
-        <v>234</v>
+        <v>180</v>
+      </c>
+      <c r="G18" t="n">
+        <v>34</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>150</v>
+      </c>
+      <c r="J18" t="n">
+        <v>56</v>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>horizontal</t>
+        </is>
+      </c>
+      <c r="L18" t="n">
+        <v>202</v>
+      </c>
+      <c r="M18" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -849,12 +1135,23 @@
       <c r="D19" t="n">
         <v>3363</v>
       </c>
-      <c r="E19" t="n">
-        <v>983</v>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>vertical</t>
+        </is>
       </c>
       <c r="F19" t="n">
         <v>189</v>
       </c>
+      <c r="G19" t="n">
+        <v>35</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
